--- a/product_upload/packages/58/file.xlsx
+++ b/product_upload/packages/58/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -834,6 +839,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>Cimuquit</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-6C6147A2FA5B</t>
         </is>
       </c>
@@ -857,7 +867,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1022,6 +1032,11 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>Cimuquit</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-7AA2F4688D07</t>
         </is>
       </c>
@@ -1045,7 +1060,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1208,6 +1223,11 @@
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>Flamex</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-6F5267249E24</t>
         </is>
       </c>
@@ -1231,7 +1251,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1394,6 +1414,11 @@
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>Flamex</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-DD15F0584464</t>
         </is>
       </c>
@@ -1417,7 +1442,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1586,6 +1611,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>Arthfre</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-31AA017F8A43</t>
         </is>
       </c>
@@ -1609,7 +1639,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1770,6 +1800,11 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>Baqsimi</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-1DC18A2C0829</t>
         </is>
       </c>
@@ -1793,7 +1828,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1950,6 +1985,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>ROVASTIN</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-948083C63B31</t>
         </is>
       </c>
@@ -1973,7 +2013,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2130,6 +2170,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>ROVASTIN</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-FE1E1A29A3CB</t>
         </is>
       </c>
@@ -2153,7 +2198,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2314,6 +2359,11 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>ROVASTIN</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-D7D0FE5E53AC</t>
         </is>
       </c>
@@ -2337,7 +2387,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2502,6 +2552,11 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>Restomap</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-73584BEC0597</t>
         </is>
       </c>
@@ -2525,7 +2580,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2682,6 +2737,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t xml:space="preserve"> Oseltamivir PPI</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-48D218E3D0AC</t>
         </is>
       </c>
@@ -2705,7 +2765,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2866,6 +2926,11 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>Oseltamivir PPI</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-78BAD898034F</t>
         </is>
       </c>
@@ -2889,7 +2954,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3046,6 +3111,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>Oseltamivir PPI</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-E15428632687</t>
         </is>
       </c>
@@ -3069,7 +3139,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3234,6 +3304,11 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>Aripro</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-D2F5BDE060DF</t>
         </is>
       </c>
@@ -3257,7 +3332,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3422,6 +3497,11 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>Provecta</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-F771CCFF76EE</t>
         </is>
       </c>
@@ -3445,7 +3525,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3610,6 +3690,11 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>Provecta</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-808E348CC5FE</t>
         </is>
       </c>
@@ -3633,7 +3718,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3794,6 +3879,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>Provecta</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-8C3B49C31D41</t>
         </is>
       </c>
@@ -3817,7 +3907,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3976,6 +4066,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>Artelac Advanced</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-71521C706B8A</t>
         </is>
       </c>
@@ -3999,7 +4094,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4156,6 +4251,11 @@
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>Glitamomet</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-0BA2CBD0F1A5</t>
         </is>
       </c>
@@ -4179,7 +4279,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4340,6 +4440,11 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>BOSULIF TABLETS</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-473A8FE1CFA1</t>
         </is>
       </c>
@@ -4363,7 +4468,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4520,6 +4625,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>BOSULIF TABLETS</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-B7829B1C7576</t>
         </is>
       </c>
@@ -4543,7 +4653,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4704,6 +4814,11 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>Perinam</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-B628BFAD5772</t>
         </is>
       </c>
@@ -4727,7 +4842,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4884,6 +4999,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>Perinam</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-BB84A3B9D2A3</t>
         </is>
       </c>
@@ -4907,7 +5027,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5068,6 +5188,11 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>Perinam</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-44B913C328E5</t>
         </is>
       </c>
@@ -5091,7 +5216,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5250,6 +5375,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>Flamotal 600 mg</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-7C01DC1FD3CC</t>
         </is>
       </c>
@@ -5273,7 +5403,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5430,6 +5560,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>Altan</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-17163496544B</t>
         </is>
       </c>
@@ -5453,7 +5588,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5610,6 +5745,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>Altan</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-8385D445A3CF</t>
         </is>
       </c>
@@ -5633,7 +5773,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5790,6 +5930,11 @@
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>daroxime</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-DFEA0CF86D86</t>
         </is>
       </c>
@@ -5813,7 +5958,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5970,6 +6115,11 @@
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>Duvalsa</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-A903FFC7E653</t>
         </is>
       </c>
@@ -5993,7 +6143,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6154,6 +6304,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>Duvalsa</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-F5EE04FD4837</t>
         </is>
       </c>
@@ -6177,7 +6332,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6338,6 +6493,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>Duvalsa</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-A30FA7F23F95</t>
         </is>
       </c>
@@ -6361,7 +6521,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6540,6 +6700,11 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>Mictonorm</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-B602E00D08FC</t>
         </is>
       </c>
@@ -6563,7 +6728,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6728,6 +6893,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>Lotemax</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-3D04708C95B9</t>
         </is>
       </c>
@@ -6751,7 +6921,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6912,6 +7082,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>Vtreat</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-BDD3F8B61783</t>
         </is>
       </c>
@@ -6935,7 +7110,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7100,6 +7275,11 @@
       </c>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>Salitav</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-A3AD36719C48</t>
         </is>
       </c>
@@ -7123,7 +7303,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7284,6 +7464,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>Salitav</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-0FFAFF2FFED5</t>
         </is>
       </c>
@@ -7307,7 +7492,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7468,6 +7653,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>Prokitav</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-7512B2CB9454</t>
         </is>
       </c>
@@ -7491,7 +7681,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7652,6 +7842,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>Prokitav</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-511B16DBAB19</t>
         </is>
       </c>
@@ -7675,7 +7870,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7836,6 +8031,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>Prokitav</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-02F4BC0A26AF</t>
         </is>
       </c>
@@ -7859,7 +8059,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8024,6 +8224,11 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>Vtreat</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-2B57B5C82AFA</t>
         </is>
       </c>
@@ -8047,7 +8252,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8212,6 +8417,11 @@
       </c>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>Anastrozole Pharmacare</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-45A47A00DA5A</t>
         </is>
       </c>
@@ -8235,7 +8445,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8404,6 +8614,11 @@
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>Warfarin ZYD</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-CDEED64E63F4</t>
         </is>
       </c>
@@ -8427,7 +8642,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8596,6 +8811,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>Warfarin ZYD</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-2A78B9CEC756</t>
         </is>
       </c>
@@ -8619,7 +8839,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8784,6 +9004,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>Warfarin ZYD</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-65A7F3FC9678</t>
         </is>
       </c>
@@ -8807,7 +9032,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -8976,6 +9201,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>Warfarin ZYD</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-D5157C0D1CF4</t>
         </is>
       </c>
@@ -8999,7 +9229,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9164,6 +9394,11 @@
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>Warfarin ZYD</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-61EF29B23BFB</t>
         </is>
       </c>
@@ -9187,7 +9422,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9348,6 +9583,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t xml:space="preserve"> Warfarin ZYD</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-F2C3197CE9D0</t>
         </is>
       </c>
@@ -9371,7 +9611,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9532,6 +9772,11 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>Sondelbay</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-3C0E37FC8F36</t>
         </is>
       </c>
@@ -9555,7 +9800,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9720,6 +9965,11 @@
       </c>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>Racad</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-D7335B7B6C09</t>
         </is>
       </c>
@@ -9743,7 +9993,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -9908,6 +10158,11 @@
       </c>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>Racad</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-89B50CDAA711</t>
         </is>
       </c>
@@ -9931,7 +10186,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10096,6 +10351,11 @@
       </c>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>VIRLAIO</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-D499C91018CF</t>
         </is>
       </c>
@@ -10119,7 +10379,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10280,6 +10540,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>Rovanzy</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-0F75B4A93F3E</t>
         </is>
       </c>
@@ -10303,7 +10568,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10472,6 +10737,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>Lyumjev Tempo Pen</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-582ECC6D246E</t>
         </is>
       </c>
@@ -10495,7 +10765,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10660,6 +10930,11 @@
       </c>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>Parlotin</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-6398D0540D0B</t>
         </is>
       </c>
@@ -10683,7 +10958,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10846,6 +11121,11 @@
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>Adzoy</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-82DD9AFCDE6F</t>
         </is>
       </c>
@@ -10869,7 +11149,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11024,6 +11304,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>Adzoy</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-A975E5530E68</t>
         </is>
       </c>
@@ -11047,7 +11332,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11208,6 +11493,11 @@
       </c>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>Laperto</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-10C840D096AE</t>
         </is>
       </c>
@@ -11231,7 +11521,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11388,6 +11678,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>Glipza</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-3BE2422E440D</t>
         </is>
       </c>
@@ -11411,7 +11706,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11574,6 +11869,11 @@
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>Lotinil</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-B1B4A23B775A</t>
         </is>
       </c>
@@ -11597,7 +11897,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11758,6 +12058,11 @@
       </c>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>Sayen</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-94E76635E34A</t>
         </is>
       </c>
@@ -11781,7 +12086,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -11942,6 +12247,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>CRONOXAM PLUS</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-72B556CF0FC3</t>
         </is>
       </c>
@@ -11965,7 +12275,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12122,6 +12432,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>CRONOXAM PLUS</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-A6B2AE836EE0</t>
         </is>
       </c>
@@ -12145,7 +12460,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12312,6 +12627,11 @@
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>Sola D3</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-435062E7CA24</t>
         </is>
       </c>
@@ -12335,7 +12655,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12504,6 +12824,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>ADOL 500 MG CAPLET</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-89C6EC2B2F66</t>
         </is>
       </c>
@@ -12527,7 +12852,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12692,6 +13017,11 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>Capitan</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-D2B68B225466</t>
         </is>
       </c>
@@ -12715,7 +13045,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12876,6 +13206,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>Capitan</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-BD00A054318A</t>
         </is>
       </c>
@@ -12899,7 +13234,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13078,6 +13413,11 @@
       </c>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>Dexorolin</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-AE1A71A8BACE</t>
         </is>
       </c>
@@ -13101,7 +13441,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13276,6 +13616,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>Dexorolin</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-0ED21FAE929C</t>
         </is>
       </c>
@@ -13299,7 +13644,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13460,6 +13805,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>Apixaban JPI</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-AED82D0CC769</t>
         </is>
       </c>
@@ -13483,7 +13833,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13644,6 +13994,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>Apixaban JPI</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-49BE5954755D</t>
         </is>
       </c>
@@ -13667,7 +14022,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13824,6 +14179,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>Apixaban JPI</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-AFC13D0F7DF0</t>
         </is>
       </c>
@@ -13847,7 +14207,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14012,6 +14372,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>Ondex</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-B489E4EB4D44</t>
         </is>
       </c>
@@ -14035,7 +14400,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14198,6 +14563,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>Evox</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-5FF342CC0481</t>
         </is>
       </c>
@@ -14221,7 +14591,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14388,6 +14758,11 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>Pentix</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-948AAC6FF1E3</t>
         </is>
       </c>
@@ -14411,7 +14786,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14574,6 +14949,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>Pentix</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-566BB44C9E29</t>
         </is>
       </c>
@@ -14597,7 +14977,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14758,6 +15138,11 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>Xadago</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-BA118B1B2794</t>
         </is>
       </c>
@@ -14781,7 +15166,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -14954,6 +15339,11 @@
       </c>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>Avocin</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-B9298DE77865</t>
         </is>
       </c>
@@ -14977,7 +15367,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15150,6 +15540,11 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>Avocin</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-1998D4F9B0C2</t>
         </is>
       </c>
@@ -15173,7 +15568,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15346,6 +15741,11 @@
       </c>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>VYZULTA</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-2143E2C3AA6C</t>
         </is>
       </c>
@@ -15369,7 +15769,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15530,6 +15930,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>Ambracy</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-11EBC7BABC2E</t>
         </is>
       </c>
@@ -15553,7 +15958,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15718,6 +16123,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>Enzular</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-3E6D85124916</t>
         </is>
       </c>
@@ -15741,7 +16151,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -15908,6 +16318,11 @@
       </c>
       <c r="AT83" t="inlineStr">
         <is>
+          <t xml:space="preserve"> Byraza Plus</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-F2C01FC346E1</t>
         </is>
       </c>
@@ -15931,7 +16346,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16096,6 +16511,11 @@
       </c>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>Ambracy</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-9523F74B4D33</t>
         </is>
       </c>
@@ -16119,7 +16539,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16282,6 +16702,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>Avotrene Emulgel</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-A64CD03F6243</t>
         </is>
       </c>
@@ -16305,7 +16730,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16462,6 +16887,11 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>Antagra</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-42C20F2DC16D</t>
         </is>
       </c>
@@ -16485,7 +16915,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16646,6 +17076,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>Antagra</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-DCCB50C36B94</t>
         </is>
       </c>
@@ -16669,7 +17104,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16830,6 +17265,11 @@
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>Domassel</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-D9B8F42FD7AD</t>
         </is>
       </c>
@@ -16853,7 +17293,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17016,6 +17456,11 @@
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>Tadalo</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-9452FD0E2199</t>
         </is>
       </c>
@@ -17039,7 +17484,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17204,6 +17649,11 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>Restomap</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-B0101D6BD477</t>
         </is>
       </c>
@@ -17227,7 +17677,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17388,6 +17838,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>Fenobat</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-1B382411ECD9</t>
         </is>
       </c>
@@ -17411,7 +17866,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17576,6 +18031,11 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>XIFAXAN</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-59C584FA12A4</t>
         </is>
       </c>
@@ -17599,7 +18059,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17772,6 +18232,11 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>Wegovy</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-6588AB39DAC0</t>
         </is>
       </c>
@@ -17795,7 +18260,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -17964,6 +18429,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>Wegovy</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-386B7FD11AAA</t>
         </is>
       </c>
@@ -17987,7 +18457,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18156,6 +18626,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>Wegovy</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-61CAA3DB462A</t>
         </is>
       </c>
@@ -18179,7 +18654,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18352,6 +18827,11 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>Wegovy</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-D1F30C2A5736</t>
         </is>
       </c>
@@ -18375,7 +18855,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18548,6 +19028,11 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>Wegovy</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-6F1673DF9145</t>
         </is>
       </c>
@@ -18571,7 +19056,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18742,6 +19227,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>SACVALY</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-E392711F9357</t>
         </is>
       </c>
@@ -18765,7 +19255,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -18936,6 +19426,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>SACVALY</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-6551B03BB7D3</t>
         </is>
       </c>
@@ -18959,7 +19454,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19130,6 +19625,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>SACVALY</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-8C9DAFAD7687</t>
         </is>
       </c>
@@ -19153,7 +19653,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19315,6 +19815,11 @@
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>Flamotal 600 mg</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-C37178EBF9FA</t>
         </is>
@@ -19331,7 +19836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19377,100 +19882,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19502,7 +20012,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19517,92 +20027,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-87517</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>327.12</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>574</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19634,7 +20149,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19649,92 +20164,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-93063</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>175.93</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>575</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19766,7 +20286,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19781,92 +20301,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-31644</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>298.19</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>576</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19898,7 +20423,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -19913,92 +20438,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-75476</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>151.77</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>577</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20030,7 +20560,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20045,92 +20575,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-90499</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>405.07</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>578</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20162,7 +20697,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20177,92 +20712,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-69249</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>107.93</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>579</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20294,7 +20834,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20309,92 +20849,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-34081</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>373.24</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>580</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20426,7 +20971,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20441,92 +20986,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-22114</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>405.37</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>581</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20558,7 +21108,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20573,92 +21123,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-15104</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>303.68</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>582</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20690,7 +21245,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20705,92 +21260,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-19135</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>198.09</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>583</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20822,7 +21382,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20837,92 +21397,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-98447</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>300.98</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>584</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20939,7 +21504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21045,6 +21610,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21080,7 +21655,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21145,6 +21720,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-7C57866B8474</t>
         </is>
@@ -21181,7 +21766,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21246,6 +21831,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-1B9A7028E1E0</t>
         </is>
@@ -21282,7 +21877,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21347,6 +21942,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-9E1748D459DD</t>
         </is>
@@ -21383,7 +21988,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21448,6 +22053,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-0F621AAF292D</t>
         </is>
@@ -21484,7 +22099,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21549,6 +22164,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-5BE899FB228D</t>
         </is>
@@ -21585,7 +22210,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21650,6 +22275,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-7588A09D49CB</t>
         </is>
@@ -21686,7 +22321,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21751,6 +22386,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-F9319234BA52</t>
         </is>
@@ -21787,7 +22432,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21852,6 +22497,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-6CD2D32521F3</t>
         </is>
@@ -21888,7 +22543,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -21953,6 +22608,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-69D2487CFD00</t>
         </is>
@@ -21989,7 +22654,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22054,6 +22719,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-E46339FB7626</t>
         </is>
@@ -22090,7 +22765,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22155,6 +22830,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-B3E232D0B233</t>
         </is>
@@ -22191,7 +22876,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22256,6 +22941,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-999941D4BEF4</t>
         </is>
@@ -22292,7 +22987,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22357,6 +23052,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-D64D15E9B6D1</t>
         </is>
@@ -22393,7 +23098,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22458,6 +23163,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-6C1F3E131F64</t>
         </is>
@@ -22494,7 +23209,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22559,6 +23274,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-270F72EC00D8</t>
         </is>
@@ -22595,7 +23320,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22660,6 +23385,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-42015854F62B</t>
         </is>
@@ -22696,7 +23431,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22761,6 +23496,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-4D2C08BD7DA2</t>
         </is>
@@ -22797,7 +23542,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -22862,6 +23607,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-080EC6C8CA91</t>
         </is>
@@ -22898,7 +23653,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -22963,6 +23718,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-605BC7E8C732</t>
         </is>
@@ -22999,7 +23764,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23064,6 +23829,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-494B4380A3EA</t>
         </is>

--- a/product_upload/packages/58/file.xlsx
+++ b/product_upload/packages/58/file.xlsx
@@ -686,8 +686,16 @@
           <t>5466565660-037-354594206373</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Cimuquit</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Cimuquit detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -875,8 +883,16 @@
           <t>1574449025-211-294924871515</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Cimuquit</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Cimuquit detailed description.</t>
+        </is>
+      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
@@ -1068,8 +1084,16 @@
           <t>8856101532-736-690302037349</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Flamex</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Flamex detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1259,8 +1283,16 @@
           <t>9692187142-098-283962334085</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Flamex</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Flamex detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1647,8 +1679,16 @@
           <t>6639576516-475-064485452313</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Baqsimi</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Baqsimi detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1836,8 +1876,16 @@
           <t>4777119085-951-107823813111</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ROVASTIN</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ROVASTIN detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -2021,8 +2069,16 @@
           <t>6872007608-082-669866612428</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ROVASTIN</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ROVASTIN detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2206,8 +2262,16 @@
           <t>9258626141-113-928072307206</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ROVASTIN</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ROVASTIN detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2395,8 +2459,16 @@
           <t>2069355013-587-449815243102</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Restomap</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Restomap detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2588,8 +2660,16 @@
           <t>5650457998-400-602601500491</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Oseltamivir PPI</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Oseltamivir PPI detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -2773,8 +2853,16 @@
           <t>2519961032-484-423993305329</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Oseltamivir PPI</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Oseltamivir PPI detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -2962,8 +3050,16 @@
           <t>1718082098-161-192535187558</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Oseltamivir PPI</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Oseltamivir PPI detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3147,8 +3243,16 @@
           <t>0576615685-476-707912429889</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Aripro</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Aripro detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -3340,8 +3444,16 @@
           <t>4516273662-659-828205817928</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Provecta</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Provecta detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -3533,8 +3645,16 @@
           <t>0447814545-936-169407991599</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Provecta</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Provecta detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -3726,8 +3846,16 @@
           <t>6037218149-849-457025114715</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Provecta</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Provecta detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -3915,8 +4043,16 @@
           <t>8902673055-832-126319637094</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Artelac Advanced</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Artelac Advanced detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4102,8 +4238,16 @@
           <t>6064636549-626-215266293492</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Glitamomet</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Glitamomet detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4287,8 +4431,16 @@
           <t>4852783962-738-486859107914</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BOSULIF TABLETS</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>BOSULIF TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -4476,8 +4628,16 @@
           <t>0063697312-678-966644933673</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BOSULIF TABLETS</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>BOSULIF TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -4661,8 +4821,16 @@
           <t>1564199761-034-325843270209</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Perinam</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Perinam detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -4850,8 +5018,16 @@
           <t>7175112064-411-520136997231</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Perinam</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Perinam detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
@@ -5035,8 +5211,16 @@
           <t>2222489256-653-631471006009</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Perinam</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Perinam detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -5224,8 +5408,16 @@
           <t>4894601857-396-010858648418</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Flamotal 600 mg</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Flamotal 600 mg detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -5411,8 +5603,16 @@
           <t>6826866816-993-185059986011</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Altan</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Altan detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -5596,8 +5796,16 @@
           <t>6469070126-435-226668736675</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Altan</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Altan detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -5781,8 +5989,16 @@
           <t>8587630370-513-468894142979</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ daroxime</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>daroxime detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -5966,8 +6182,16 @@
           <t>4426882415-015-198019508023</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Duvalsa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Duvalsa detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -6151,8 +6375,16 @@
           <t>1038522012-026-786052355806</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Duvalsa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Duvalsa detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -6340,8 +6572,16 @@
           <t>9082340138-797-412934910767</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Duvalsa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Duvalsa detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6929,8 +7169,16 @@
           <t>6999355062-657-591962170249</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Vtreat</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Vtreat detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -7118,8 +7366,16 @@
           <t>4625931673-989-022928140326</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Salitav</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Salitav detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7311,8 +7567,16 @@
           <t>2962966235-075-847665230547</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Salitav</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Salitav detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -7500,8 +7764,16 @@
           <t>5693612093-268-710749726015</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Prokitav</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Prokitav detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -7689,8 +7961,16 @@
           <t>4966075114-900-016303665687</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Prokitav</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Prokitav detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
@@ -7878,8 +8158,16 @@
           <t>7515470544-096-872046717393</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Prokitav</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Prokitav detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -8067,8 +8355,16 @@
           <t>5034363123-998-711780288516</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Vtreat</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Vtreat detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -8260,8 +8556,16 @@
           <t>9001469101-118-983429820322</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Anastrozole Pharmacare</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Anastrozole Pharmacare detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -9430,8 +9734,16 @@
           <t>1459301910-595-662401540266</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Warfarin ZYD</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Warfarin ZYD detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
@@ -9619,8 +9931,16 @@
           <t>3322572452-289-323743667323</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sondelbay</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sondelbay detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -9808,8 +10128,16 @@
           <t>5674004076-156-744976812348</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Racad</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Racad detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -10001,8 +10329,16 @@
           <t>5812961843-302-904946969267</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Racad</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Racad detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -10194,8 +10530,16 @@
           <t>9494478231-559-095758750840</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIRLAIO</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>VIRLAIO detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10387,8 +10731,16 @@
           <t>4186620835-537-605436164377</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rovanzy</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Rovanzy detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10773,8 +11125,16 @@
           <t>6473088656-370-492053938691</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Parlotin</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Parlotin detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -10966,8 +11326,16 @@
           <t>3422115951-593-211712100843</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Adzoy</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Adzoy detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -11157,8 +11525,16 @@
           <t>3931029341-645-293535152938</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Adzoy</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Adzoy detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -11340,8 +11716,16 @@
           <t>0901063607-043-674458046595</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Laperto</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Laperto detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11529,8 +11913,16 @@
           <t>7119204832-727-807282885907</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Glipza</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Glipza detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -11905,8 +12297,16 @@
           <t>1721533433-790-311441212099</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sayen</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sayen detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -12094,8 +12494,16 @@
           <t>2504894310-259-326093232104</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CRONOXAM PLUS</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>CRONOXAM PLUS detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -12283,8 +12691,16 @@
           <t>6816040421-165-278388913378</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CRONOXAM PLUS</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>CRONOXAM PLUS detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -12468,8 +12884,16 @@
           <t>2872235998-043-078370738430</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sola D3</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sola D3 detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -12860,8 +13284,16 @@
           <t>3615965308-226-140414729138</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Capitan</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Capitan detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -13053,8 +13485,16 @@
           <t>5797831076-039-060319635011</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Capitan</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Capitan detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13652,8 +14092,16 @@
           <t>7371254333-302-970976476849</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Apixaban JPI</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Apixaban JPI detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -13841,8 +14289,16 @@
           <t>3494621709-576-549951515195</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Apixaban JPI</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Apixaban JPI detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -14030,8 +14486,16 @@
           <t>9476119771-702-013103922140</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Apixaban JPI</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Apixaban JPI detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -14408,8 +14872,16 @@
           <t>5475296278-251-264162778423</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Evox</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Evox detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
@@ -14599,8 +15071,16 @@
           <t>1365757247-083-884766948937</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pentix</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Pentix detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -14794,8 +15274,16 @@
           <t>9511786358-177-874647759779</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pentix</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Pentix detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
@@ -14985,8 +15473,16 @@
           <t>9752667560-369-173126223836</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Xadago</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Xadago detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -15777,8 +16273,16 @@
           <t>1363600130-056-475363595846</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ambracy</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Ambracy detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -15966,8 +16470,16 @@
           <t>6472019224-012-637399865071</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Enzular</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Enzular detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -16159,8 +16671,16 @@
           <t>6086042551-619-226653242352</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Byraza Plus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Byraza Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -16354,8 +16874,16 @@
           <t>0856926434-835-075781628211</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ambracy</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Ambracy detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16738,8 +17266,16 @@
           <t>4985443875-156-033848327109</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Antagra</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Antagra detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -16923,8 +17459,16 @@
           <t>2134169915-140-796598067067</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Antagra</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Antagra detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -17112,8 +17656,16 @@
           <t>5919088692-696-361716591371</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Domassel</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Domassel detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17301,8 +17853,16 @@
           <t>1317013476-536-797859964384</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tadalo</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Tadalo detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -17492,8 +18052,16 @@
           <t>9639787479-549-612370946709</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Restomap</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Restomap detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -17685,8 +18253,16 @@
           <t>5178595384-011-673804042094</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Fenobat</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Fenobat detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -17874,8 +18450,16 @@
           <t>9766559061-210-822049701577</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ XIFAXAN</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>XIFAXAN detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -19661,8 +20245,16 @@
           <t>0773657075-890-716651674106</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Flamotal 600 mg</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Flamotal 600 mg detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/58/file.xlsx
+++ b/product_upload/packages/58/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20474,7 +20474,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22096,7 +22096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22177,40 +22177,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22290,38 +22295,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>336.37</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-7C57866B8474</t>
         </is>
@@ -22401,38 +22411,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>418.57</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-1B9A7028E1E0</t>
         </is>
@@ -22512,38 +22527,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>271.21</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-9E1748D459DD</t>
         </is>
@@ -22623,38 +22643,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>38.67</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-0F621AAF292D</t>
         </is>
@@ -22734,38 +22759,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>40.7</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-5BE899FB228D</t>
         </is>
@@ -22845,38 +22875,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>281.87</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-7588A09D49CB</t>
         </is>
@@ -22956,38 +22991,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>90.28</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-F9319234BA52</t>
         </is>
@@ -23067,38 +23107,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>122.58</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-6CD2D32521F3</t>
         </is>
@@ -23178,38 +23223,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>126.96</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-69D2487CFD00</t>
         </is>
@@ -23289,38 +23339,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>280.61</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-E46339FB7626</t>
         </is>
@@ -23400,38 +23455,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>39.47</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-B3E232D0B233</t>
         </is>
@@ -23511,38 +23571,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>438.19</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-999941D4BEF4</t>
         </is>
@@ -23622,38 +23687,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>86.8</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-D64D15E9B6D1</t>
         </is>
@@ -23733,38 +23803,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>244.9</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-6C1F3E131F64</t>
         </is>
@@ -23844,38 +23919,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>81.56999999999999</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-270F72EC00D8</t>
         </is>
@@ -23955,38 +24035,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>378.56</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-42015854F62B</t>
         </is>
@@ -24066,38 +24151,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>269.68</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-4D2C08BD7DA2</t>
         </is>
@@ -24177,38 +24267,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>63.78</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-080EC6C8CA91</t>
         </is>
@@ -24288,38 +24383,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>395.06</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-605BC7E8C732</t>
         </is>
@@ -24399,38 +24499,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>148.61</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-494B4380A3EA</t>
         </is>
